--- a/smartshop/EvidenceBasedAdaptiveUI/reports/AdaptiveRepository/repository_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/AdaptiveRepository/repository_summary.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1009,22 +1009,22 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -1033,10 +1033,10 @@
         <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -1048,10 +1048,10 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -1063,19 +1063,19 @@
         <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
         <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
         <v>3</v>
